--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_HAMPSHIRE_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_HAMPSHIRE_2021.xlsx
@@ -1381,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="D57">
-        <v>0.09352517985611511</v>
+        <v>0.09352517985611512</v>
       </c>
     </row>
     <row r="58">
